--- a/artfynd/A 26449-2026 artfynd.xlsx
+++ b/artfynd/A 26449-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,41 +675,44 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73598064</v>
+        <v>73598049</v>
       </c>
       <c r="B2" t="n">
-        <v>88921</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87375</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5741</v>
+        <v>3739</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -717,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547847.3153233643</v>
+        <v>547848</v>
       </c>
       <c r="R2" t="n">
-        <v>6314207.291473799</v>
+        <v>6314206</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,19 +753,9 @@
           <t>2018-09-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-09-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,41 +783,44 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73598082</v>
+        <v>73598076</v>
       </c>
       <c r="B3" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -832,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547779.9331659644</v>
+        <v>547770</v>
       </c>
       <c r="R3" t="n">
-        <v>6314224.504992018</v>
+        <v>6314215</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +861,9 @@
           <t>2018-09-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-09-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,15 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73598076</v>
+        <v>96975442</v>
       </c>
       <c r="B4" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,21 +902,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -945,20 +926,21 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
+          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547770.2092114356</v>
+        <v>547826</v>
       </c>
       <c r="R4" t="n">
-        <v>6314215.126142709</v>
+        <v>6314172</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,22 +967,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-09-29</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-09-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,22 +993,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73598049</v>
+        <v>73597722</v>
       </c>
       <c r="B5" t="n">
-        <v>85301</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,33 +1011,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3739</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1078,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547848.4201589656</v>
+        <v>547956</v>
       </c>
       <c r="R5" t="n">
-        <v>6314206.213954397</v>
+        <v>6314158</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,19 +1070,9 @@
           <t>2018-09-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-09-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,6 +1097,2013 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>73597757</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>547952</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6314152</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2018-09-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2018-09-29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>97372912</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bölnegård, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>547949</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6314243</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>96975326</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91424</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5733</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Såpfingersvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ramaria lutea</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Vent.) Schild</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>547914</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6314159</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>73597761</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91409</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>547952</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6314152</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2018-09-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2018-09-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>73598064</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91409</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>547847</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6314207</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2018-09-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2018-09-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>96975284</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91409</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>547934</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6314170</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>73597718</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>547956</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6314158</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2018-09-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2018-09-29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>73597755</v>
+      </c>
+      <c r="B13" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>547952</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6314152</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2018-09-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2018-09-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>73598082</v>
+      </c>
+      <c r="B14" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>547780</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6314225</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2018-09-29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2018-09-29</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>96975288</v>
+      </c>
+      <c r="B15" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>547934</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6314170</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>97372911</v>
+      </c>
+      <c r="B16" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bölnegård, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>547949</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6314243</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>73597728</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92567</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>547956</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6314158</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2018-09-29</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2018-09-29</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>73597716</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>547956</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6314158</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2018-09-29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2018-09-29</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>73597749</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>547954</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6314152</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2018-09-29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2018-09-29</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>73597769</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>547907</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6314156</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2018-09-29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2018-09-29</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>96975333</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>547911</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6314152</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>73597740</v>
+      </c>
+      <c r="B22" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>547954</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6314152</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2018-09-29</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2018-09-29</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>96975329</v>
+      </c>
+      <c r="B23" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>547911</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6314152</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>73597760</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>547952</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6314152</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2018-09-29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2018-09-29</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26449-2026 artfynd.xlsx
+++ b/artfynd/A 26449-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ24"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96975442</v>
+        <v>136495630</v>
       </c>
       <c r="B4" t="n">
-        <v>93197</v>
+        <v>93391</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,45 +917,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
+          <t>Fröseke, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547826</v>
+        <v>547885</v>
       </c>
       <c r="R4" t="n">
-        <v>6314172</v>
+        <v>6314189</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,12 +982,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,27 +1003,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
+          <t>Joakim Andersson Hemberg, karin folkesson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96975442</t>
+          <t>https://artportalen.se/Sighting/136495630</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73597722</v>
+        <v>96975442</v>
       </c>
       <c r="B5" t="n">
-        <v>93209</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,36 +1031,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
+          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547956</v>
+        <v>547826</v>
       </c>
       <c r="R5" t="n">
-        <v>6314158</v>
+        <v>6314172</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,12 +1096,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-09-29</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-09-29</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,19 +1122,19 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73597722</t>
+          <t>https://artportalen.se/Sighting/96975442</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>73597757</v>
+        <v>73597722</v>
       </c>
       <c r="B6" t="n">
         <v>93209</v>
@@ -1162,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547952</v>
+        <v>547956</v>
       </c>
       <c r="R6" t="n">
-        <v>6314152</v>
+        <v>6314158</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,13 +1233,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73597757</t>
+          <t>https://artportalen.se/Sighting/73597722</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97372912</v>
+        <v>73597757</v>
       </c>
       <c r="B7" t="n">
         <v>93209</v>
@@ -1258,28 +1267,19 @@
           <t>Banker</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bölnegård, Sm</t>
+          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>547949</v>
+        <v>547952</v>
       </c>
       <c r="R7" t="n">
-        <v>6314243</v>
+        <v>6314152</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2018-09-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2018-09-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,22 +1332,22 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97372912</t>
+          <t>https://artportalen.se/Sighting/73597757</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96975326</v>
+        <v>97372912</v>
       </c>
       <c r="B8" t="n">
-        <v>91424</v>
+        <v>93209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1355,21 +1355,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5733</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1386,14 +1386,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
+          <t>Bölnegård, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>547914</v>
+        <v>547949</v>
       </c>
       <c r="R8" t="n">
-        <v>6314159</v>
+        <v>6314243</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,22 +1446,22 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
+          <t>Tobias Ivarsson, Jenny Ivarsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96975326</t>
+          <t>https://artportalen.se/Sighting/97372912</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>73597761</v>
+        <v>96975326</v>
       </c>
       <c r="B9" t="n">
-        <v>91409</v>
+        <v>91424</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,36 +1469,45 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5741</v>
+        <v>5733</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Vent.) Schild</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
+          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>547952</v>
+        <v>547914</v>
       </c>
       <c r="R9" t="n">
-        <v>6314152</v>
+        <v>6314159</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,12 +1534,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2018-09-29</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2018-09-29</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,19 +1560,19 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73597761</t>
+          <t>https://artportalen.se/Sighting/96975326</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>73598064</v>
+        <v>73597761</v>
       </c>
       <c r="B10" t="n">
         <v>91409</v>
@@ -1600,10 +1609,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>547847</v>
+        <v>547952</v>
       </c>
       <c r="R10" t="n">
-        <v>6314207</v>
+        <v>6314152</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1662,13 +1671,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73598064</t>
+          <t>https://artportalen.se/Sighting/73597761</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96975284</v>
+        <v>73598064</v>
       </c>
       <c r="B11" t="n">
         <v>91409</v>
@@ -1696,28 +1705,19 @@
           <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
+          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>547934</v>
+        <v>547847</v>
       </c>
       <c r="R11" t="n">
-        <v>6314170</v>
+        <v>6314207</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2018-09-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2018-09-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,22 +1770,22 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96975284</t>
+          <t>https://artportalen.se/Sighting/73598064</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>73597718</v>
+        <v>96975284</v>
       </c>
       <c r="B12" t="n">
-        <v>93233</v>
+        <v>91409</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1793,36 +1793,45 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>5741</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
+          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547956</v>
+        <v>547934</v>
       </c>
       <c r="R12" t="n">
-        <v>6314158</v>
+        <v>6314170</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,12 +1858,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2018-09-29</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2018-09-29</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1875,19 +1884,19 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73597718</t>
+          <t>https://artportalen.se/Sighting/96975284</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>73597755</v>
+        <v>73597718</v>
       </c>
       <c r="B13" t="n">
         <v>93233</v>
@@ -1924,10 +1933,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547952</v>
+        <v>547956</v>
       </c>
       <c r="R13" t="n">
-        <v>6314152</v>
+        <v>6314158</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1986,13 +1995,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73597755</t>
+          <t>https://artportalen.se/Sighting/73597718</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>73598082</v>
+        <v>73597755</v>
       </c>
       <c r="B14" t="n">
         <v>93233</v>
@@ -2029,10 +2038,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547780</v>
+        <v>547952</v>
       </c>
       <c r="R14" t="n">
-        <v>6314225</v>
+        <v>6314152</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2091,13 +2100,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73598082</t>
+          <t>https://artportalen.se/Sighting/73597755</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>96975288</v>
+        <v>73598082</v>
       </c>
       <c r="B15" t="n">
         <v>93233</v>
@@ -2125,28 +2134,19 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
+          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547934</v>
+        <v>547780</v>
       </c>
       <c r="R15" t="n">
-        <v>6314170</v>
+        <v>6314225</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2018-09-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2018-09-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2199,19 +2199,19 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96975288</t>
+          <t>https://artportalen.se/Sighting/73598082</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>97372911</v>
+        <v>96975288</v>
       </c>
       <c r="B16" t="n">
         <v>93233</v>
@@ -2253,14 +2253,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bölnegård, Sm</t>
+          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547949</v>
+        <v>547934</v>
       </c>
       <c r="R16" t="n">
-        <v>6314243</v>
+        <v>6314170</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2313,59 +2313,68 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson</t>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97372911</t>
+          <t>https://artportalen.se/Sighting/96975288</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>73597728</v>
+        <v>97372911</v>
       </c>
       <c r="B17" t="n">
-        <v>92567</v>
+        <v>93233</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6031</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
+          <t>Bölnegård, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547956</v>
+        <v>547949</v>
       </c>
       <c r="R17" t="n">
-        <v>6314158</v>
+        <v>6314243</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2392,12 +2401,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2018-09-29</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2018-09-29</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2418,59 +2427,49 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jenny Ivarsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73597728</t>
+          <t>https://artportalen.se/Sighting/97372911</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>73597716</v>
+        <v>73597728</v>
       </c>
       <c r="B18" t="n">
-        <v>99118</v>
+        <v>92567</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
@@ -2539,13 +2538,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73597716</t>
+          <t>https://artportalen.se/Sighting/73597728</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>73597749</v>
+        <v>73597716</v>
       </c>
       <c r="B19" t="n">
         <v>99118</v>
@@ -2575,7 +2574,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2592,10 +2591,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547954</v>
+        <v>547956</v>
       </c>
       <c r="R19" t="n">
-        <v>6314152</v>
+        <v>6314158</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2654,13 +2653,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73597749</t>
+          <t>https://artportalen.se/Sighting/73597716</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>73597769</v>
+        <v>73597749</v>
       </c>
       <c r="B20" t="n">
         <v>99118</v>
@@ -2690,7 +2689,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2707,10 +2706,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547907</v>
+        <v>547954</v>
       </c>
       <c r="R20" t="n">
-        <v>6314156</v>
+        <v>6314152</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2769,13 +2768,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73597769</t>
+          <t>https://artportalen.se/Sighting/73597749</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>96975333</v>
+        <v>73597769</v>
       </c>
       <c r="B21" t="n">
         <v>99118</v>
@@ -2805,7 +2804,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2818,14 +2817,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
+          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547911</v>
+        <v>547907</v>
       </c>
       <c r="R21" t="n">
-        <v>6314152</v>
+        <v>6314156</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2852,12 +2851,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2018-09-29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2018-09-29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2878,49 +2877,49 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96975333</t>
+          <t>https://artportalen.se/Sighting/73597769</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>73597740</v>
+        <v>96975333</v>
       </c>
       <c r="B22" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2933,11 +2932,11 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
+          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547954</v>
+        <v>547911</v>
       </c>
       <c r="R22" t="n">
         <v>6314152</v>
@@ -2967,12 +2966,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2018-09-29</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2018-09-29</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2993,19 +2992,19 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73597740</t>
+          <t>https://artportalen.se/Sighting/96975333</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>96975329</v>
+        <v>73597740</v>
       </c>
       <c r="B23" t="n">
         <v>106244</v>
@@ -3035,7 +3034,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3048,11 +3047,11 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
+          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547911</v>
+        <v>547954</v>
       </c>
       <c r="R23" t="n">
         <v>6314152</v>
@@ -3082,12 +3081,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2018-09-29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2018-09-29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3108,22 +3107,22 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96975329</t>
+          <t>https://artportalen.se/Sighting/73597740</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>73597760</v>
+        <v>96975329</v>
       </c>
       <c r="B24" t="n">
-        <v>101326</v>
+        <v>106244</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3131,35 +3130,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
+          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>547952</v>
+        <v>547911</v>
       </c>
       <c r="R24" t="n">
         <v>6314152</v>
@@ -3189,12 +3196,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2018-09-29</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2018-09-29</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3215,11 +3222,118 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96975329</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>73597760</v>
+      </c>
+      <c r="B25" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>547952</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6314152</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2018-09-29</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2018-09-29</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/73597760</t>
         </is>
@@ -3250,6 +3364,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26449-2026 artfynd.xlsx
+++ b/artfynd/A 26449-2026 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>136495630</v>
       </c>
       <c r="B4" t="n">
-        <v>93391</v>
+        <v>93392</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
